--- a/output/【河洛話注音】證人得獎感言.xlsx
+++ b/output/【河洛話注音】證人得獎感言.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\work\Piau-Im\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC768011-E67B-4DA7-AD2B-063BFE242817}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA9FEDDF-EA41-4FC9-B696-354EF0F23406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3420" yWindow="3420" windowWidth="21480" windowHeight="11895" firstSheet="1" activeTab="1" xr2:uid="{34E700FC-4C0E-994F-B0CD-4AD13BB7FCE5}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{34E700FC-4C0E-994F-B0CD-4AD13BB7FCE5}"/>
   </bookViews>
   <sheets>
     <sheet name="閩拼拼音" sheetId="17" r:id="rId1"/>
@@ -2812,9 +2812,6 @@
 </t>
   </si>
   <si>
-    <t>&lt;div class='zhu_yin'&gt;&lt;p class='title'&gt;</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;證&lt;/rb&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rt&gt;ㄐㄧㄥ˪&lt;/rt&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
   </si>
   <si>
@@ -4756,6 +4753,9 @@
   </si>
   <si>
     <t xml:space="preserve">  &lt;ruby&gt;&lt;rb&gt;頂&lt;/rb&gt;&lt;rt&gt;ting2&lt;/rt&gt;&lt;rp&gt;(&lt;/rp&gt;&lt;rtc&gt;ㄉㄧㄥˋ&lt;/rtc&gt;&lt;rp&gt;)&lt;/rp&gt;&lt;/ruby&gt;</t>
+  </si>
+  <si>
+    <t>&lt;div class='Piau_Im'&gt;&lt;p class='title'&gt;</t>
   </si>
 </sst>
 </file>
@@ -14482,12 +14482,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1385</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1386</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -14497,12 +14497,12 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -14512,22 +14512,22 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>1392</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -14542,27 +14542,27 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>1396</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -14572,17 +14572,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -14592,17 +14592,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>1401</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -14622,52 +14622,52 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>1407</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1410</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>1411</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -14677,117 +14677,117 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -14802,22 +14802,22 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -14827,72 +14827,72 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>1438</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -14912,7 +14912,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -14922,42 +14922,42 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>1451</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -14967,87 +14967,87 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="111" spans="1:1">
       <c r="A111" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="115" spans="1:1">
@@ -15057,32 +15057,32 @@
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -15092,57 +15092,57 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>1476</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>1477</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="133" spans="1:1">
       <c r="A133" s="1" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="134" spans="1:1">
@@ -15157,27 +15157,27 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -15187,17 +15187,17 @@
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="1" t="s">
-        <v>1395</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -15207,12 +15207,12 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -15222,12 +15222,12 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="151" spans="1:1">
@@ -15237,12 +15237,12 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="153" spans="1:1">
       <c r="A153" s="1" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="154" spans="1:1">
@@ -15252,42 +15252,42 @@
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="1" t="s">
-        <v>1490</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>1491</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="1" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="1" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="1" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="1" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="163" spans="1:1">
@@ -15297,57 +15297,57 @@
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="1" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="1" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="1" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="1" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="175" spans="1:1">
@@ -15362,17 +15362,17 @@
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="1" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="1" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="180" spans="1:1">
@@ -15397,22 +15397,22 @@
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="1" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="1" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -15422,32 +15422,32 @@
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="191" spans="1:1">
       <c r="A191" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="192" spans="1:1">
       <c r="A192" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1" t="s">
-        <v>1508</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="195" spans="1:1">
@@ -15457,22 +15457,22 @@
     </row>
     <row r="196" spans="1:1">
       <c r="A196" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="197" spans="1:1">
       <c r="A197" s="1" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="1" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="200" spans="1:1">
@@ -15482,22 +15482,22 @@
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="1" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="1" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="205" spans="1:1">
@@ -15507,22 +15507,22 @@
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="1" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="1" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="1" t="s">
-        <v>1515</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="1" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="210" spans="1:1">
@@ -15532,27 +15532,27 @@
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="1" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="1" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="1" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="216" spans="1:1">
@@ -15562,57 +15562,57 @@
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="1" t="s">
-        <v>1393</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="1" t="s">
-        <v>1471</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="219" spans="1:1">
       <c r="A219" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="1" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="1" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="1" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="1" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="225" spans="1:1">
       <c r="A225" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="227" spans="1:1">
       <c r="A227" s="1" t="s">
-        <v>1409</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="228" spans="1:1">
@@ -15622,42 +15622,42 @@
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="1" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="1" t="s">
-        <v>1443</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="1" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="1" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="1" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="1" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="1" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="1" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="237" spans="1:1">
@@ -15667,52 +15667,52 @@
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="1" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="1" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="1" t="s">
-        <v>1408</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="1" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="1" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="248" spans="1:1">
@@ -15722,17 +15722,17 @@
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="1" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="1" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="1" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="252" spans="1:1">
@@ -15742,47 +15742,47 @@
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="1" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="1" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="1" t="s">
-        <v>1405</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="257" spans="1:1">
       <c r="A257" s="1" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="1" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="1" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="1" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="1" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="262" spans="1:1">
@@ -15792,67 +15792,67 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="1" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="1" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="1" t="s">
-        <v>1414</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="1" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="1" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="1" t="s">
-        <v>1402</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="1" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="1" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="1" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="1" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="275" spans="1:1">
       <c r="A275" s="1" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="276" spans="1:1">
@@ -15872,32 +15872,32 @@
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="1" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="1" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="1" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="285" spans="1:1">
@@ -15907,62 +15907,62 @@
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="1" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="1" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="1" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="1" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="1" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="1" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="1" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="1" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="296" spans="1:1">
       <c r="A296" s="1" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="1" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="298" spans="1:1">
@@ -16001,12 +16001,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -16016,12 +16016,12 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -16031,22 +16031,22 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -16061,27 +16061,27 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -16091,17 +16091,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -16111,17 +16111,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -16141,37 +16141,37 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -16181,12 +16181,12 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -16196,117 +16196,117 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -16321,22 +16321,22 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -16346,72 +16346,72 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -16431,7 +16431,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -16441,42 +16441,42 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -16486,67 +16486,67 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -16556,17 +16556,17 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="115" spans="1:1">
@@ -16576,32 +16576,32 @@
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -16611,52 +16611,52 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -16676,27 +16676,27 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -16706,17 +16706,17 @@
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="1" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -16726,12 +16726,12 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -16741,12 +16741,12 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="151" spans="1:1">
@@ -16756,7 +16756,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -16771,42 +16771,42 @@
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="1" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="1" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="1" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="1" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="163" spans="1:1">
@@ -16816,57 +16816,57 @@
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="1" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="1" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="1" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="1" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="175" spans="1:1">
@@ -16881,17 +16881,17 @@
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="1" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="1" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="180" spans="1:1">
@@ -16916,22 +16916,22 @@
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="1" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="1" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -16941,12 +16941,12 @@
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="191" spans="1:1">
@@ -16961,12 +16961,12 @@
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="195" spans="1:1">
@@ -16986,12 +16986,12 @@
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="1" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="200" spans="1:1">
@@ -17001,22 +17001,22 @@
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="1" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="1" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="205" spans="1:1">
@@ -17026,22 +17026,22 @@
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="1" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="1" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="1" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="210" spans="1:1">
@@ -17051,27 +17051,27 @@
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="1" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="1" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="1" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="216" spans="1:1">
@@ -17081,12 +17081,12 @@
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="1" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="1" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="219" spans="1:1">
@@ -17096,27 +17096,27 @@
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="1" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="1" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="1" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="225" spans="1:1">
@@ -17126,7 +17126,7 @@
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="227" spans="1:1">
@@ -17141,42 +17141,42 @@
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="1" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="1" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="1" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="1" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="1" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="1" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="1" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="1" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="237" spans="1:1">
@@ -17186,52 +17186,52 @@
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="1" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="1" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="1" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="1" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="248" spans="1:1">
@@ -17241,17 +17241,17 @@
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="1" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="1" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="1" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="252" spans="1:1">
@@ -17261,22 +17261,22 @@
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="1" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="1" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="257" spans="1:1">
@@ -17286,22 +17286,22 @@
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="1" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="1" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="1" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="1" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="262" spans="1:1">
@@ -17311,62 +17311,62 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="1" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="1" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="1" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="1" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="1" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="1" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="1" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="1" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="1" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -17391,32 +17391,32 @@
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="1" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="1" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="1" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="285" spans="1:1">
@@ -17426,52 +17426,52 @@
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="1" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1381</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="1" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="1" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="1" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="1" t="s">
-        <v>1383</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="1" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="1" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="1" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -17481,7 +17481,7 @@
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="1" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="298" spans="1:1">
@@ -17520,12 +17520,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -17535,7 +17535,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -17555,7 +17555,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -17565,7 +17565,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -17610,7 +17610,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -17620,7 +17620,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -17630,17 +17630,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -17660,7 +17660,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -17675,12 +17675,12 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -17705,7 +17705,7 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -17715,7 +17715,7 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -17730,17 +17730,17 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="46" spans="1:1">
@@ -17760,7 +17760,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -17770,7 +17770,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -17790,12 +17790,12 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -17805,7 +17805,7 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -17825,7 +17825,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -17840,7 +17840,7 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -17850,12 +17850,12 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -17865,12 +17865,12 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -17880,7 +17880,7 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -17890,7 +17890,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -17910,27 +17910,27 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -17950,7 +17950,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -17965,7 +17965,7 @@
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -17975,12 +17975,12 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="94" spans="1:1">
@@ -17990,7 +17990,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -18005,7 +18005,7 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -18020,7 +18020,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -18030,7 +18030,7 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="104" spans="1:1">
@@ -18060,12 +18060,12 @@
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -18100,7 +18100,7 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -18110,7 +18110,7 @@
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -18135,7 +18135,7 @@
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -18145,12 +18145,12 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -18160,7 +18160,7 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="130" spans="1:1">
@@ -18175,7 +18175,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -18195,7 +18195,7 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -18210,7 +18210,7 @@
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="140" spans="1:1">
@@ -18245,7 +18245,7 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="147" spans="1:1">
@@ -18295,7 +18295,7 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="157" spans="1:1">
@@ -18315,7 +18315,7 @@
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="161" spans="1:1">
@@ -18335,7 +18335,7 @@
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="165" spans="1:1">
@@ -18365,12 +18365,12 @@
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="172" spans="1:1">
@@ -18380,7 +18380,7 @@
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="174" spans="1:1">
@@ -18405,7 +18405,7 @@
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -18440,7 +18440,7 @@
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="186" spans="1:1">
@@ -18450,7 +18450,7 @@
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -18460,12 +18460,12 @@
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="191" spans="1:1">
@@ -18480,12 +18480,12 @@
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="195" spans="1:1">
@@ -18520,22 +18520,22 @@
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="1" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="1" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="205" spans="1:1">
@@ -18545,7 +18545,7 @@
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="1" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="207" spans="1:1">
@@ -18570,12 +18570,12 @@
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="1" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="213" spans="1:1">
@@ -18605,7 +18605,7 @@
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="1" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="219" spans="1:1">
@@ -18625,17 +18625,17 @@
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="1" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="1" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="1" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="225" spans="1:1">
@@ -18645,7 +18645,7 @@
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="227" spans="1:1">
@@ -18660,12 +18660,12 @@
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="1" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="231" spans="1:1">
@@ -18675,7 +18675,7 @@
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="1" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="233" spans="1:1">
@@ -18705,17 +18705,17 @@
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="1" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="241" spans="1:1">
@@ -18740,12 +18740,12 @@
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="247" spans="1:1">
@@ -18765,12 +18765,12 @@
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="1" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="1" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="252" spans="1:1">
@@ -18780,7 +18780,7 @@
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="1" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="254" spans="1:1">
@@ -18790,7 +18790,7 @@
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="1" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="256" spans="1:1">
@@ -18810,7 +18810,7 @@
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="1" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="260" spans="1:1">
@@ -18830,7 +18830,7 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="264" spans="1:1">
@@ -18845,7 +18845,7 @@
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="1" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="267" spans="1:1">
@@ -18855,12 +18855,12 @@
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="1" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="1" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="270" spans="1:1">
@@ -18870,7 +18870,7 @@
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="272" spans="1:1">
@@ -18885,7 +18885,7 @@
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -18925,17 +18925,17 @@
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="285" spans="1:1">
@@ -18950,17 +18950,17 @@
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="1" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="290" spans="1:1">
@@ -18970,7 +18970,7 @@
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="1" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="292" spans="1:1">
@@ -18990,7 +18990,7 @@
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="1" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -19039,12 +19039,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -19054,7 +19054,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -19074,7 +19074,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -19084,7 +19084,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -19129,7 +19129,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -19139,7 +19139,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -19149,17 +19149,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -19179,7 +19179,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -19194,12 +19194,12 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -19224,7 +19224,7 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -19234,7 +19234,7 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -19249,22 +19249,22 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1146</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -19279,7 +19279,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -19289,7 +19289,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -19304,17 +19304,17 @@
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>1147</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>1148</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -19324,7 +19324,7 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -19344,7 +19344,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -19359,7 +19359,7 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -19369,12 +19369,12 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -19384,12 +19384,12 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -19399,7 +19399,7 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -19409,7 +19409,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>1153</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -19429,27 +19429,27 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -19469,7 +19469,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -19484,7 +19484,7 @@
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -19494,12 +19494,12 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="94" spans="1:1">
@@ -19509,7 +19509,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -19524,7 +19524,7 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -19539,7 +19539,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -19549,7 +19549,7 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="104" spans="1:1">
@@ -19579,12 +19579,12 @@
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -19619,7 +19619,7 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -19629,7 +19629,7 @@
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -19654,7 +19654,7 @@
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -19664,12 +19664,12 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -19679,7 +19679,7 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="130" spans="1:1">
@@ -19694,7 +19694,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -19714,7 +19714,7 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -19724,12 +19724,12 @@
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="140" spans="1:1">
@@ -19764,7 +19764,7 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="147" spans="1:1">
@@ -19814,7 +19814,7 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="157" spans="1:1">
@@ -19834,7 +19834,7 @@
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="161" spans="1:1">
@@ -19854,7 +19854,7 @@
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="165" spans="1:1">
@@ -19884,12 +19884,12 @@
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="172" spans="1:1">
@@ -19899,7 +19899,7 @@
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="174" spans="1:1">
@@ -19924,7 +19924,7 @@
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -19959,7 +19959,7 @@
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="1" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="186" spans="1:1">
@@ -19969,7 +19969,7 @@
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -19979,12 +19979,12 @@
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="191" spans="1:1">
@@ -19999,12 +19999,12 @@
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="195" spans="1:1">
@@ -20039,22 +20039,22 @@
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="205" spans="1:1">
@@ -20064,7 +20064,7 @@
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="1" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="207" spans="1:1">
@@ -20089,12 +20089,12 @@
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="213" spans="1:1">
@@ -20124,7 +20124,7 @@
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="219" spans="1:1">
@@ -20144,17 +20144,17 @@
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="225" spans="1:1">
@@ -20164,7 +20164,7 @@
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="227" spans="1:1">
@@ -20179,12 +20179,12 @@
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="231" spans="1:1">
@@ -20194,7 +20194,7 @@
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="233" spans="1:1">
@@ -20224,17 +20224,17 @@
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="241" spans="1:1">
@@ -20259,12 +20259,12 @@
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="247" spans="1:1">
@@ -20284,12 +20284,12 @@
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="252" spans="1:1">
@@ -20299,7 +20299,7 @@
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="254" spans="1:1">
@@ -20309,7 +20309,7 @@
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="1" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="256" spans="1:1">
@@ -20329,7 +20329,7 @@
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="260" spans="1:1">
@@ -20349,7 +20349,7 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="264" spans="1:1">
@@ -20364,7 +20364,7 @@
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="267" spans="1:1">
@@ -20374,12 +20374,12 @@
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="270" spans="1:1">
@@ -20389,7 +20389,7 @@
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="1" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="272" spans="1:1">
@@ -20404,7 +20404,7 @@
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -20444,17 +20444,17 @@
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="285" spans="1:1">
@@ -20469,17 +20469,17 @@
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="290" spans="1:1">
@@ -20489,7 +20489,7 @@
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="292" spans="1:1">
@@ -20509,7 +20509,7 @@
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -20558,12 +20558,12 @@
   <sheetData>
     <row r="1" spans="1:1" ht="204">
       <c r="A1" s="1" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -20573,7 +20573,7 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="5" spans="1:1">
@@ -20593,7 +20593,7 @@
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="9" spans="1:1">
@@ -20603,7 +20603,7 @@
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -20648,7 +20648,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="20" spans="1:1">
@@ -20658,7 +20658,7 @@
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -20668,17 +20668,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -20698,7 +20698,7 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="30" spans="1:1">
@@ -20713,12 +20713,12 @@
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="34" spans="1:1">
@@ -20743,7 +20743,7 @@
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -20753,7 +20753,7 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="41" spans="1:1">
@@ -20768,22 +20768,22 @@
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="47" spans="1:1">
@@ -20798,7 +20798,7 @@
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="50" spans="1:1">
@@ -20808,7 +20808,7 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="52" spans="1:1">
@@ -20828,12 +20828,12 @@
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="57" spans="1:1">
@@ -20843,7 +20843,7 @@
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="59" spans="1:1">
@@ -20863,7 +20863,7 @@
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -20878,7 +20878,7 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="66" spans="1:1">
@@ -20888,12 +20888,12 @@
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -20903,12 +20903,12 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="72" spans="1:1">
@@ -20918,7 +20918,7 @@
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="74" spans="1:1">
@@ -20928,7 +20928,7 @@
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="76" spans="1:1">
@@ -20948,27 +20948,27 @@
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -20988,7 +20988,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -21003,7 +21003,7 @@
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="91" spans="1:1">
@@ -21013,12 +21013,12 @@
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="94" spans="1:1">
@@ -21028,7 +21028,7 @@
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="96" spans="1:1">
@@ -21043,7 +21043,7 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="99" spans="1:1">
@@ -21058,7 +21058,7 @@
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="102" spans="1:1">
@@ -21068,7 +21068,7 @@
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="104" spans="1:1">
@@ -21098,12 +21098,12 @@
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -21138,7 +21138,7 @@
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="118" spans="1:1">
@@ -21148,7 +21148,7 @@
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="120" spans="1:1">
@@ -21173,7 +21173,7 @@
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="125" spans="1:1">
@@ -21183,12 +21183,12 @@
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="128" spans="1:1">
@@ -21198,7 +21198,7 @@
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="130" spans="1:1">
@@ -21213,7 +21213,7 @@
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -21233,7 +21233,7 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="137" spans="1:1">
@@ -21248,7 +21248,7 @@
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="140" spans="1:1">
@@ -21283,7 +21283,7 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="147" spans="1:1">
@@ -21333,7 +21333,7 @@
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="157" spans="1:1">
@@ -21353,7 +21353,7 @@
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="161" spans="1:1">
@@ -21373,7 +21373,7 @@
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="165" spans="1:1">
@@ -21403,12 +21403,12 @@
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="172" spans="1:1">
@@ -21418,7 +21418,7 @@
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="174" spans="1:1">
@@ -21443,7 +21443,7 @@
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="179" spans="1:1">
@@ -21478,7 +21478,7 @@
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="1" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="186" spans="1:1">
@@ -21488,7 +21488,7 @@
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -21498,12 +21498,12 @@
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="191" spans="1:1">
@@ -21518,12 +21518,12 @@
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="195" spans="1:1">
@@ -21558,22 +21558,22 @@
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="1" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="1" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="205" spans="1:1">
@@ -21583,7 +21583,7 @@
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="207" spans="1:1">
@@ -21608,12 +21608,12 @@
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="1" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="213" spans="1:1">
@@ -21643,7 +21643,7 @@
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="219" spans="1:1">
@@ -21653,7 +21653,7 @@
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="1" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="221" spans="1:1">
@@ -21663,17 +21663,17 @@
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="1" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="1" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="225" spans="1:1">
@@ -21683,7 +21683,7 @@
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="227" spans="1:1">
@@ -21698,12 +21698,12 @@
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="1" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="231" spans="1:1">
@@ -21713,7 +21713,7 @@
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="1" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="233" spans="1:1">
@@ -21743,17 +21743,17 @@
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="1" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="241" spans="1:1">
@@ -21778,12 +21778,12 @@
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="1" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="247" spans="1:1">
@@ -21803,12 +21803,12 @@
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="1" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="252" spans="1:1">
@@ -21818,7 +21818,7 @@
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="1" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="254" spans="1:1">
@@ -21828,7 +21828,7 @@
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="256" spans="1:1">
@@ -21848,7 +21848,7 @@
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="260" spans="1:1">
@@ -21868,7 +21868,7 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="1" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="264" spans="1:1">
@@ -21883,7 +21883,7 @@
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="267" spans="1:1">
@@ -21893,12 +21893,12 @@
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="1" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="270" spans="1:1">
@@ -21908,7 +21908,7 @@
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="272" spans="1:1">
@@ -21923,7 +21923,7 @@
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -21963,17 +21963,17 @@
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="285" spans="1:1">
@@ -21988,17 +21988,17 @@
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="290" spans="1:1">
@@ -22008,7 +22008,7 @@
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="292" spans="1:1">
@@ -22028,7 +22028,7 @@
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -22082,7 +22082,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>912</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -22092,12 +22092,12 @@
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="6" spans="1:1">
@@ -22107,22 +22107,22 @@
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="11" spans="1:1">
@@ -22137,27 +22137,27 @@
     </row>
     <row r="13" spans="1:1">
       <c r="A13" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="18" spans="1:1">
@@ -22167,17 +22167,17 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="22" spans="1:1">
@@ -22187,17 +22187,17 @@
     </row>
     <row r="23" spans="1:1">
       <c r="A23" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="26" spans="1:1">
@@ -22217,37 +22217,37 @@
     </row>
     <row r="29" spans="1:1">
       <c r="A29" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="36" spans="1:1">
@@ -22257,12 +22257,12 @@
     </row>
     <row r="37" spans="1:1">
       <c r="A37" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="39" spans="1:1">
@@ -22272,117 +22272,117 @@
     </row>
     <row r="40" spans="1:1">
       <c r="A40" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" s="1" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="63" spans="1:1">
@@ -22397,22 +22397,22 @@
     </row>
     <row r="65" spans="1:1">
       <c r="A65" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="69" spans="1:1">
@@ -22422,72 +22422,72 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="84" spans="1:1">
@@ -22507,7 +22507,7 @@
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="88" spans="1:1">
@@ -22517,42 +22517,42 @@
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="97" spans="1:1">
@@ -22562,67 +22562,67 @@
     </row>
     <row r="98" spans="1:1">
       <c r="A98" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="102" spans="1:1">
       <c r="A102" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="103" spans="1:1">
       <c r="A103" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="104" spans="1:1">
       <c r="A104" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="105" spans="1:1">
       <c r="A105" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="106" spans="1:1">
       <c r="A106" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="107" spans="1:1">
       <c r="A107" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="108" spans="1:1">
       <c r="A108" s="1" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="109" spans="1:1">
       <c r="A109" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="110" spans="1:1">
       <c r="A110" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="111" spans="1:1">
@@ -22632,17 +22632,17 @@
     </row>
     <row r="112" spans="1:1">
       <c r="A112" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="113" spans="1:1">
       <c r="A113" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="114" spans="1:1">
       <c r="A114" s="1" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="115" spans="1:1">
@@ -22652,32 +22652,32 @@
     </row>
     <row r="116" spans="1:1">
       <c r="A116" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="117" spans="1:1">
       <c r="A117" s="1" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="118" spans="1:1">
       <c r="A118" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="119" spans="1:1">
       <c r="A119" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="120" spans="1:1">
       <c r="A120" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="121" spans="1:1">
       <c r="A121" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="122" spans="1:1">
@@ -22687,52 +22687,52 @@
     </row>
     <row r="123" spans="1:1">
       <c r="A123" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="124" spans="1:1">
       <c r="A124" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="125" spans="1:1">
       <c r="A125" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="126" spans="1:1">
       <c r="A126" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="127" spans="1:1">
       <c r="A127" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="128" spans="1:1">
       <c r="A128" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="129" spans="1:1">
       <c r="A129" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="130" spans="1:1">
       <c r="A130" s="1" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="131" spans="1:1">
       <c r="A131" s="1" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="132" spans="1:1">
       <c r="A132" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="133" spans="1:1">
@@ -22752,27 +22752,27 @@
     </row>
     <row r="136" spans="1:1">
       <c r="A136" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="137" spans="1:1">
       <c r="A137" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="138" spans="1:1">
       <c r="A138" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="139" spans="1:1">
       <c r="A139" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="140" spans="1:1">
       <c r="A140" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="141" spans="1:1">
@@ -22782,17 +22782,17 @@
     </row>
     <row r="142" spans="1:1">
       <c r="A142" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="143" spans="1:1">
       <c r="A143" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="144" spans="1:1">
       <c r="A144" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="145" spans="1:1">
@@ -22802,12 +22802,12 @@
     </row>
     <row r="146" spans="1:1">
       <c r="A146" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="147" spans="1:1">
       <c r="A147" s="1" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="148" spans="1:1">
@@ -22817,12 +22817,12 @@
     </row>
     <row r="149" spans="1:1">
       <c r="A149" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="150" spans="1:1">
       <c r="A150" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="151" spans="1:1">
@@ -22832,7 +22832,7 @@
     </row>
     <row r="152" spans="1:1">
       <c r="A152" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="153" spans="1:1">
@@ -22847,42 +22847,42 @@
     </row>
     <row r="155" spans="1:1">
       <c r="A155" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="156" spans="1:1">
       <c r="A156" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="157" spans="1:1">
       <c r="A157" s="1" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="158" spans="1:1">
       <c r="A158" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="159" spans="1:1">
       <c r="A159" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="160" spans="1:1">
       <c r="A160" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="161" spans="1:1">
       <c r="A161" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="162" spans="1:1">
       <c r="A162" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="163" spans="1:1">
@@ -22892,57 +22892,57 @@
     </row>
     <row r="164" spans="1:1">
       <c r="A164" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="165" spans="1:1">
       <c r="A165" s="1" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="166" spans="1:1">
       <c r="A166" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="167" spans="1:1">
       <c r="A167" s="1" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="168" spans="1:1">
       <c r="A168" s="1" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="169" spans="1:1">
       <c r="A169" s="1" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="170" spans="1:1">
       <c r="A170" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="171" spans="1:1">
       <c r="A171" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="172" spans="1:1">
       <c r="A172" s="1" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="173" spans="1:1">
       <c r="A173" s="1" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="174" spans="1:1">
       <c r="A174" s="1" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="175" spans="1:1">
@@ -22957,17 +22957,17 @@
     </row>
     <row r="177" spans="1:1">
       <c r="A177" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="178" spans="1:1">
       <c r="A178" s="1" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="179" spans="1:1">
       <c r="A179" s="1" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="180" spans="1:1">
@@ -22992,22 +22992,22 @@
     </row>
     <row r="184" spans="1:1">
       <c r="A184" s="1" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="185" spans="1:1">
       <c r="A185" s="1" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="186" spans="1:1">
       <c r="A186" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="187" spans="1:1">
       <c r="A187" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="188" spans="1:1">
@@ -23017,12 +23017,12 @@
     </row>
     <row r="189" spans="1:1">
       <c r="A189" s="1" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="190" spans="1:1">
       <c r="A190" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="191" spans="1:1">
@@ -23037,12 +23037,12 @@
     </row>
     <row r="193" spans="1:1">
       <c r="A193" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="194" spans="1:1">
       <c r="A194" s="1" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="195" spans="1:1">
@@ -23062,12 +23062,12 @@
     </row>
     <row r="198" spans="1:1">
       <c r="A198" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="199" spans="1:1">
       <c r="A199" s="1" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="200" spans="1:1">
@@ -23077,22 +23077,22 @@
     </row>
     <row r="201" spans="1:1">
       <c r="A201" s="1" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="202" spans="1:1">
       <c r="A202" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="203" spans="1:1">
       <c r="A203" s="1" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="204" spans="1:1">
       <c r="A204" s="1" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="205" spans="1:1">
@@ -23102,22 +23102,22 @@
     </row>
     <row r="206" spans="1:1">
       <c r="A206" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="207" spans="1:1">
       <c r="A207" s="1" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="208" spans="1:1">
       <c r="A208" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="209" spans="1:1">
       <c r="A209" s="1" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="210" spans="1:1">
@@ -23127,27 +23127,27 @@
     </row>
     <row r="211" spans="1:1">
       <c r="A211" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="212" spans="1:1">
       <c r="A212" s="1" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="213" spans="1:1">
       <c r="A213" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="214" spans="1:1">
       <c r="A214" s="1" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="215" spans="1:1">
       <c r="A215" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="216" spans="1:1">
@@ -23157,12 +23157,12 @@
     </row>
     <row r="217" spans="1:1">
       <c r="A217" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="218" spans="1:1">
       <c r="A218" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="219" spans="1:1">
@@ -23172,27 +23172,27 @@
     </row>
     <row r="220" spans="1:1">
       <c r="A220" s="1" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="221" spans="1:1">
       <c r="A221" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="222" spans="1:1">
       <c r="A222" s="1" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="223" spans="1:1">
       <c r="A223" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="224" spans="1:1">
       <c r="A224" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="225" spans="1:1">
@@ -23202,7 +23202,7 @@
     </row>
     <row r="226" spans="1:1">
       <c r="A226" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="227" spans="1:1">
@@ -23217,42 +23217,42 @@
     </row>
     <row r="229" spans="1:1">
       <c r="A229" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="230" spans="1:1">
       <c r="A230" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="231" spans="1:1">
       <c r="A231" s="1" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="232" spans="1:1">
       <c r="A232" s="1" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="233" spans="1:1">
       <c r="A233" s="1" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="234" spans="1:1">
       <c r="A234" s="1" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="235" spans="1:1">
       <c r="A235" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="236" spans="1:1">
       <c r="A236" s="1" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="237" spans="1:1">
@@ -23262,52 +23262,52 @@
     </row>
     <row r="238" spans="1:1">
       <c r="A238" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="239" spans="1:1">
       <c r="A239" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="240" spans="1:1">
       <c r="A240" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="241" spans="1:1">
       <c r="A241" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="242" spans="1:1">
       <c r="A242" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="243" spans="1:1">
       <c r="A243" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="244" spans="1:1">
       <c r="A244" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="245" spans="1:1">
       <c r="A245" s="1" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="246" spans="1:1">
       <c r="A246" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="247" spans="1:1">
       <c r="A247" s="1" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="248" spans="1:1">
@@ -23317,17 +23317,17 @@
     </row>
     <row r="249" spans="1:1">
       <c r="A249" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="250" spans="1:1">
       <c r="A250" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="251" spans="1:1">
       <c r="A251" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="252" spans="1:1">
@@ -23337,22 +23337,22 @@
     </row>
     <row r="253" spans="1:1">
       <c r="A253" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="254" spans="1:1">
       <c r="A254" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="255" spans="1:1">
       <c r="A255" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="256" spans="1:1">
       <c r="A256" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="257" spans="1:1">
@@ -23362,22 +23362,22 @@
     </row>
     <row r="258" spans="1:1">
       <c r="A258" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="259" spans="1:1">
       <c r="A259" s="1" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="260" spans="1:1">
       <c r="A260" s="1" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="261" spans="1:1">
       <c r="A261" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="262" spans="1:1">
@@ -23387,62 +23387,62 @@
     </row>
     <row r="263" spans="1:1">
       <c r="A263" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="264" spans="1:1">
       <c r="A264" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="265" spans="1:1">
       <c r="A265" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="266" spans="1:1">
       <c r="A266" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="267" spans="1:1">
       <c r="A267" s="1" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="268" spans="1:1">
       <c r="A268" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="269" spans="1:1">
       <c r="A269" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="270" spans="1:1">
       <c r="A270" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="271" spans="1:1">
       <c r="A271" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="272" spans="1:1">
       <c r="A272" s="1" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="273" spans="1:1">
       <c r="A273" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="274" spans="1:1">
       <c r="A274" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="275" spans="1:1">
@@ -23467,32 +23467,32 @@
     </row>
     <row r="279" spans="1:1">
       <c r="A279" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="280" spans="1:1">
       <c r="A280" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="281" spans="1:1">
       <c r="A281" s="1" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="282" spans="1:1">
       <c r="A282" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="283" spans="1:1">
       <c r="A283" s="1" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="284" spans="1:1">
       <c r="A284" s="1" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="285" spans="1:1">
@@ -23502,52 +23502,52 @@
     </row>
     <row r="286" spans="1:1">
       <c r="A286" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="287" spans="1:1">
       <c r="A287" s="1" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="288" spans="1:1">
       <c r="A288" s="1" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="289" spans="1:1">
       <c r="A289" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="290" spans="1:1">
       <c r="A290" s="1" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="291" spans="1:1">
       <c r="A291" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="292" spans="1:1">
       <c r="A292" s="1" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="293" spans="1:1">
       <c r="A293" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="294" spans="1:1">
       <c r="A294" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="295" spans="1:1">
       <c r="A295" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="296" spans="1:1">
@@ -23557,7 +23557,7 @@
     </row>
     <row r="297" spans="1:1">
       <c r="A297" s="1" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="298" spans="1:1">
